--- a/artfynd/A 31082-2024 artfynd.xlsx
+++ b/artfynd/A 31082-2024 artfynd.xlsx
@@ -2354,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119549301</v>
+        <v>119549289</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,35 +2366,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2402,7 +2405,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579767</v>
+        <v>579733</v>
       </c>
       <c r="R17" t="n">
         <v>6426032</v>
@@ -2465,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119549106</v>
+        <v>119549301</v>
       </c>
       <c r="B18" t="n">
-        <v>56522</v>
+        <v>97907</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2477,39 +2480,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2517,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579748</v>
+        <v>579767</v>
       </c>
       <c r="R18" t="n">
-        <v>6426050</v>
+        <v>6426032</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,17 +2554,13 @@
           <t>2024-09-04</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Nyligen fälld fjäder</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2584,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119549289</v>
+        <v>119549106</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,34 +2595,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2635,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579733</v>
+        <v>579748</v>
       </c>
       <c r="R19" t="n">
-        <v>6426032</v>
+        <v>6426050</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,13 +2669,17 @@
           <t>2024-09-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Nyligen fälld fjäder</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31082-2024 artfynd.xlsx
+++ b/artfynd/A 31082-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119528933</v>
+        <v>119528905</v>
       </c>
       <c r="B2" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579752</v>
+        <v>579750</v>
       </c>
       <c r="R2" t="n">
-        <v>6426032</v>
+        <v>6426075</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119528981</v>
+        <v>119529053</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,39 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579791</v>
+        <v>579737</v>
       </c>
       <c r="R3" t="n">
-        <v>6426018</v>
+        <v>6426017</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119528960</v>
+        <v>119529032</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -944,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579790</v>
+        <v>579742</v>
       </c>
       <c r="R4" t="n">
-        <v>6426015</v>
+        <v>6425995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1235,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119528918</v>
+        <v>119528933</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,33 +1251,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579754</v>
+        <v>579752</v>
       </c>
       <c r="R7" t="n">
-        <v>6426040</v>
+        <v>6426032</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119529053</v>
+        <v>119528981</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,38 +1358,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1397,13 +1398,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579737</v>
+        <v>579791</v>
       </c>
       <c r="R8" t="n">
-        <v>6426017</v>
+        <v>6426018</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1442,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1685,7 +1685,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119528905</v>
+        <v>119528960</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579750</v>
+        <v>579790</v>
       </c>
       <c r="R11" t="n">
-        <v>6426075</v>
+        <v>6426015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119528944</v>
+        <v>119528918</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579759</v>
+        <v>579754</v>
       </c>
       <c r="R12" t="n">
-        <v>6426061</v>
+        <v>6426040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119529032</v>
+        <v>119528944</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579742</v>
+        <v>579759</v>
       </c>
       <c r="R13" t="n">
-        <v>6425995</v>
+        <v>6426061</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,10 +2018,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119549313</v>
+        <v>119549090</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,35 +2030,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2066,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579754</v>
+        <v>579763</v>
       </c>
       <c r="R14" t="n">
-        <v>6425997</v>
+        <v>6426034</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119549090</v>
+        <v>119549253</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,38 +2144,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579763</v>
+        <v>579749</v>
       </c>
       <c r="R15" t="n">
-        <v>6426034</v>
+        <v>6426043</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119549253</v>
+        <v>119549313</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579749</v>
+        <v>579754</v>
       </c>
       <c r="R16" t="n">
-        <v>6426043</v>
+        <v>6425997</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119549106</v>
+        <v>119549346</v>
       </c>
       <c r="B19" t="n">
-        <v>56522</v>
+        <v>91836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,35 +2595,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>4363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2631,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579748</v>
+        <v>579778</v>
       </c>
       <c r="R19" t="n">
-        <v>6426050</v>
+        <v>6425960</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2669,17 +2668,13 @@
           <t>2024-09-04</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Nyligen fälld fjäder</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2698,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119549346</v>
+        <v>119549106</v>
       </c>
       <c r="B20" t="n">
-        <v>91836</v>
+        <v>56522</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2714,34 +2709,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4363</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2749,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579778</v>
+        <v>579748</v>
       </c>
       <c r="R20" t="n">
-        <v>6425960</v>
+        <v>6426050</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2787,13 +2783,17 @@
           <t>2024-09-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Nyligen fälld fjäder</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31082-2024 artfynd.xlsx
+++ b/artfynd/A 31082-2024 artfynd.xlsx
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119549253</v>
+        <v>119549106</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>56522</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2144,35 +2144,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2180,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579749</v>
+        <v>579748</v>
       </c>
       <c r="R15" t="n">
-        <v>6426043</v>
+        <v>6426050</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,13 +2222,17 @@
           <t>2024-09-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Nyligen fälld fjäder</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2243,7 +2251,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119549313</v>
+        <v>119549253</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2291,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579754</v>
+        <v>579749</v>
       </c>
       <c r="R16" t="n">
-        <v>6425997</v>
+        <v>6426043</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,10 +2362,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119549289</v>
+        <v>119549346</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91836</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,21 +2378,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2405,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579733</v>
+        <v>579778</v>
       </c>
       <c r="R17" t="n">
-        <v>6426032</v>
+        <v>6425960</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119549301</v>
+        <v>119549289</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2480,35 +2488,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2516,7 +2527,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579767</v>
+        <v>579733</v>
       </c>
       <c r="R18" t="n">
         <v>6426032</v>
@@ -2579,10 +2590,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119549346</v>
+        <v>119549313</v>
       </c>
       <c r="B19" t="n">
-        <v>91836</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,38 +2602,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4363</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2630,10 +2638,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579778</v>
+        <v>579754</v>
       </c>
       <c r="R19" t="n">
-        <v>6425960</v>
+        <v>6425997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119549106</v>
+        <v>119549301</v>
       </c>
       <c r="B20" t="n">
-        <v>56522</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,39 +2713,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2745,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579748</v>
+        <v>579767</v>
       </c>
       <c r="R20" t="n">
-        <v>6426050</v>
+        <v>6426032</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,17 +2787,13 @@
           <t>2024-09-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Nyligen fälld fjäder</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
